--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486384_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486384_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5139</v>
+        <v>5.9563</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5217</v>
+        <v>4.6895</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9922</v>
+        <v>1.2668</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6423</v>
+        <v>6.9125</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7273</v>
+        <v>4.8391</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9149</v>
+        <v>2.0734</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5524</v>
+        <v>5.9485</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4272</v>
+        <v>4.6448</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1253</v>
+        <v>1.3037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.964</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6998</v>
+        <v>0.1943</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7897</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0875</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R2" t="n">
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4111</v>
+        <v>-0.9986</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2259</v>
+        <v>-0.2139</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1852</v>
+        <v>-0.7847</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1805</v>
+        <v>5.9554</v>
       </c>
       <c r="E3" t="n">
-        <v>4.037</v>
+        <v>4.994</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1435</v>
+        <v>0.9614</v>
       </c>
       <c r="G3" t="n">
-        <v>6.9125</v>
+        <v>4.6423</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8391</v>
+        <v>1.7273</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0734</v>
+        <v>2.9149</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9485</v>
+        <v>4.5524</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6448</v>
+        <v>2.4272</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3037</v>
+        <v>2.1253</v>
       </c>
       <c r="M3" t="n">
-        <v>0.964</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1943</v>
+        <v>-0.6998</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.7897</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0875</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7744</v>
+        <v>0.0303</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.2464</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.908</v>
+        <v>-0.216</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7003</v>
+        <v>3.106</v>
       </c>
       <c r="E4" t="n">
-        <v>3.632</v>
+        <v>3.2535</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0683</v>
+        <v>-0.1475</v>
       </c>
       <c r="G4" t="n">
         <v>3.4756</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9197</v>
+        <v>0.3254</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6321</v>
+        <v>0.2536</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2876</v>
+        <v>0.0718</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5078</v>
+        <v>2.9752</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5571</v>
+        <v>4.1786</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0493</v>
+        <v>-1.2034</v>
       </c>
       <c r="G5" t="n">
         <v>4.0283</v>
@@ -844,13 +844,13 @@
         <v>0.2175</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1098</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4146</v>
+        <v>0.0361</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6952</v>
+        <v>0.5411</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7602</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1539</v>
+        <v>2.3352</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5328</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6211</v>
+        <v>1.5595</v>
       </c>
       <c r="G6" t="n">
         <v>0.1379</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>1.711</v>
+        <v>0.8923</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4697</v>
+        <v>0.7126</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2413</v>
+        <v>0.1796</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1376</v>
+        <v>1.442</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4854</v>
+        <v>0.8207</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6521</v>
+        <v>0.6213</v>
       </c>
       <c r="G7" t="n">
         <v>0.6101</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3426</v>
+        <v>-0.0382</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1815</v>
+        <v>0.1538</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1612</v>
+        <v>-0.192</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.588</v>
+        <v>-0.3692</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5398</v>
+        <v>-1.1361</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9518</v>
+        <v>0.7669</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7832</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1099</v>
+        <v>-0.8911</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3305</v>
+        <v>0.0733</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7794</v>
+        <v>-0.9644</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9841</v>
+        <v>-0.5017</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6847</v>
+        <v>2.0397</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2993</v>
+        <v>-2.5414</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4053</v>
+        <v>1.9091</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3437</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.749</v>
+        <v>2.4902</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4005</v>
+        <v>3.0672</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4777</v>
+        <v>0.3682</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8781</v>
+        <v>2.699</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0049</v>
+        <v>-1.1581</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1339</v>
+        <v>-0.9493</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1291</v>
+        <v>-0.2088</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8615</v>
+        <v>0.0667</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4795</v>
+        <v>0.0601</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.382</v>
+        <v>0.0066</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3698</v>
+        <v>-2.2599</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1474</v>
+        <v>-0.773</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4557</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.603</v>
+        <v>-0.2685</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9091</v>
+        <v>-0.4053</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.3437</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4902</v>
+        <v>-0.749</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0672</v>
+        <v>-0.4005</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3682</v>
+        <v>0.4777</v>
       </c>
       <c r="L10" t="n">
-        <v>2.699</v>
+        <v>-0.8781</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1581</v>
+        <v>-0.0049</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9493</v>
+        <v>-0.1339</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2088</v>
+        <v>0.1291</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.579</v>
+        <v>-0.6504</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5239</v>
+        <v>-0.2992</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0551</v>
+        <v>-0.3512</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2599</v>
+        <v>-0.3698</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2599</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3066</v>
+        <v>-0.9414</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9165</v>
+        <v>-1.7363</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6099</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.9931</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1697</v>
+        <v>-0.8045</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2499</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9198</v>
+        <v>-0.7348</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6302</v>
+        <v>-3.6196</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9049</v>
+        <v>-3.1716</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7254</v>
+        <v>-0.4479</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6902</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5926</v>
+        <v>-0.5819</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1971</v>
+        <v>-0.0697</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7896</v>
+        <v>-0.5122</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.5377</v>
+        <v>15.5652</v>
       </c>
       <c r="E13" t="n">
-        <v>13.1758</v>
+        <v>14.2032</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3619</v>
+        <v>1.362100000000001</v>
       </c>
       <c r="G13" t="n">
         <v>19.8302</v>
@@ -1438,7 +1438,7 @@
         <v>10.6901</v>
       </c>
       <c r="I13" t="n">
-        <v>9.139899999999999</v>
+        <v>9.139900000000001</v>
       </c>
       <c r="J13" t="n">
         <v>17.7597</v>
@@ -1447,7 +1447,7 @@
         <v>12.7911</v>
       </c>
       <c r="L13" t="n">
-        <v>4.9686</v>
+        <v>4.968600000000001</v>
       </c>
       <c r="M13" t="n">
         <v>2.0705</v>
@@ -1456,22 +1456,22 @@
         <v>-2.1009</v>
       </c>
       <c r="O13" t="n">
-        <v>4.171399999999999</v>
+        <v>4.1714</v>
       </c>
       <c r="P13" t="n">
-        <v>3.262500000000001</v>
+        <v>3.2625</v>
       </c>
       <c r="Q13" t="n">
         <v>-6.5251</v>
       </c>
       <c r="R13" t="n">
-        <v>9.7875</v>
+        <v>9.787499999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.100300000000001</v>
+        <v>-2.0729</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1441</v>
+        <v>0.8834000000000002</v>
       </c>
       <c r="U13" t="n">
         <v>-2.9562</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1441</v>
+        <v>2.7876</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4603</v>
+        <v>4.3485</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3162</v>
+        <v>-1.5609</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7359</v>
@@ -1546,13 +1546,13 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0324</v>
+        <v>0.6111</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5997</v>
+        <v>0.4879</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6321</v>
+        <v>0.1232</v>
       </c>
       <c r="V14" t="n">
         <v>2.2599</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3081</v>
+        <v>1.9838</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6555</v>
+        <v>4.8791</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3474</v>
+        <v>-2.8953</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4212</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2277</v>
+        <v>0.4479</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3016</v>
+        <v>0.5252</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5294</v>
+        <v>-0.0772</v>
       </c>
       <c r="V15" t="n">
         <v>1.3045</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8621</v>
+        <v>1.2539</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0996</v>
+        <v>1.4349</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2375</v>
+        <v>-0.181</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7217</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0189</v>
+        <v>0.4107</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3064</v>
+        <v>0.0288</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3253</v>
+        <v>0.3818</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8246</v>
+        <v>0.6037</v>
       </c>
       <c r="E17" t="n">
         <v>1.3559</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5314</v>
+        <v>-0.7522</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4818</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.3906</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2019</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8133</v>
+        <v>0.5924</v>
       </c>
       <c r="V17" t="n">
         <v>1.695</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3277</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2103</v>
+        <v>0.4302</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.538</v>
+        <v>-0.964</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9447</v>
+        <v>-3.6403</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0858</v>
+        <v>-2.1103</v>
       </c>
       <c r="I18" t="n">
-        <v>0.141</v>
+        <v>-1.53</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0298</v>
+        <v>-0.7052</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1063</v>
+        <v>-0.3825</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0765</v>
+        <v>-0.3227</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9149</v>
+        <v>-2.9351</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9794</v>
+        <v>-1.7278</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0645</v>
+        <v>-1.2073</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>1.312</v>
+        <v>0.6937</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2402</v>
+        <v>0.0277</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.666</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2534</v>
+        <v>-0.628</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4682</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2148</v>
+        <v>0.0862</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0511</v>
+        <v>-0.7758</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2647</v>
+        <v>-0.073</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2136</v>
+        <v>-0.7028</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0182</v>
+        <v>0.4754</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0182</v>
+        <v>1.3719</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.8964</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0694</v>
+        <v>-1.2512</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2829</v>
+        <v>-1.4449</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2136</v>
+        <v>0.1936</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9728</v>
+        <v>0.3653</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6886</v>
+        <v>-0.1021</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2842</v>
+        <v>0.4675</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2995</v>
+        <v>-1.0226</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0169</v>
+        <v>0.428</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2826</v>
+        <v>-1.4506</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6403</v>
+        <v>-0.9447</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1103</v>
+        <v>-1.0858</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.53</v>
+        <v>0.141</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7052</v>
+        <v>-0.0298</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3825</v>
+        <v>-0.1063</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3227</v>
+        <v>0.0765</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9351</v>
+        <v>-0.9149</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7278</v>
+        <v>-0.9794</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2073</v>
+        <v>0.0645</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.6171</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4194</v>
+        <v>0.4579</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3474</v>
+        <v>0.1592</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5248</v>
+        <v>-1.6558</v>
       </c>
       <c r="E21" t="n">
-        <v>0.409</v>
+        <v>0.1855</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9338</v>
+        <v>-1.8413</v>
       </c>
       <c r="G21" t="n">
         <v>-1.133</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7382</v>
+        <v>0.6072</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8256</v>
+        <v>0.6021</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7571</v>
+        <v>-1.7428</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.273</v>
+        <v>-1.8035</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4841</v>
+        <v>0.0607</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7758</v>
+        <v>-0.0511</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.073</v>
+        <v>-0.2647</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7028</v>
+        <v>0.2136</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4754</v>
+        <v>0.0182</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3719</v>
+        <v>0.0182</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8964</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2512</v>
+        <v>-0.0694</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4449</v>
+        <v>-0.2829</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1936</v>
+        <v>0.2136</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7638</v>
+        <v>0.4834</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6609</v>
+        <v>0.3533</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1029</v>
+        <v>0.1301</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0648</v>
+        <v>-4.8355</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.139</v>
+        <v>-4.3567</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9258</v>
+        <v>-0.4788</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2817</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8256</v>
+        <v>0.4038</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0288</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0721</v>
+        <v>0.3749</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.4493</v>
+        <v>-7.7679</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5255</v>
+        <v>-6.4195</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9238</v>
+        <v>-1.3484</v>
       </c>
       <c r="G24" t="n">
         <v>-6.6429</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3686</v>
+        <v>1.05</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6427</v>
+        <v>0.7487</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2741</v>
+        <v>0.3013</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.5377</v>
+        <v>-11.5574</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2319999999999993</v>
+        <v>-0.2318000000000007</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.3058</v>
+        <v>-11.3256</v>
       </c>
       <c r="G25" t="n">
         <v>-19.8301</v>
@@ -2392,7 +2392,7 @@
         <v>-12.7911</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.9687</v>
+        <v>-4.968699999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-3.2628</v>
@@ -2404,13 +2404,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1004</v>
+        <v>6.080799999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9563</v>
+        <v>2.9564</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1441000000000002</v>
+        <v>3.1243</v>
       </c>
       <c r="V25" t="n">
         <v>5.4546</v>
